--- a/data/detallesBasedatosPrueba.xlsx
+++ b/data/detallesBasedatosPrueba.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="16.7109375" customWidth="1" min="1" max="1"/>
@@ -1518,6 +1518,162 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>784578</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ALEXANDER FRANCISO TIBANTA MIRANDA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1447586991001</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1447758691</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PLANILLA DE APORTES</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>12,25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>25,47</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>33,00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Dr. Christian Santiago Izurieta Cruz</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Dr.Enrique Alberto Molestina Molestiina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>784577</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ALEXANDER FRANCISO TIBANTA MIRANDA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1447586991001</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1447758691</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PLANILLA DE APORTES</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>45,35</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>125,36</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>162,00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dr. Christian Santiago Izurieta Cruz</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Dr.Enrique Alberto Molestina Molestiina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>784574</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ALEXANDER FRANCISO TIBANTA MIRANDA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1447586991001</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1447758691</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PLANILLA DE APORTES</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>145,99</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>225,84</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>293,00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Dr. Christian Santiago Izurieta Cruz</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Dr.Enrique Alberto Molestina Molestiina</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
